--- a/diseases/d108/1990-1994.xlsx
+++ b/diseases/d108/1990-1994.xlsx
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9793,7 +9793,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12583,7 +12583,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13383,7 +13383,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15383,7 +15383,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15783,7 +15783,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16183,7 +16183,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17373,7 +17373,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18573,7 +18573,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18973,7 +18973,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19373,7 +19373,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19773,7 +19773,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20173,7 +20173,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20973,7 +20973,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21373,7 +21373,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -22163,7 +22163,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22963,7 +22963,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23763,7 +23763,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24163,7 +24163,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24563,7 +24563,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24963,7 +24963,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25363,7 +25363,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25763,7 +25763,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26163,7 +26163,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26563,7 +26563,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">

--- a/diseases/d108/1990-1994.xlsx
+++ b/diseases/d108/1990-1994.xlsx
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9793,7 +9793,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12583,7 +12583,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13383,7 +13383,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15383,7 +15383,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15783,7 +15783,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16183,7 +16183,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17373,7 +17373,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17773,7 +17773,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18573,7 +18573,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18973,7 +18973,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19373,7 +19373,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19773,7 +19773,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20173,7 +20173,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20973,7 +20973,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21373,7 +21373,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -22163,7 +22163,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22963,7 +22963,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23763,7 +23763,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24163,7 +24163,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24563,7 +24563,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24963,7 +24963,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25363,7 +25363,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25763,7 +25763,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26163,7 +26163,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26563,7 +26563,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
